--- a/VerveStacks_UGA_grids_kan/source_data/VerveStacks_UGA.xlsx
+++ b/VerveStacks_UGA_grids_kan/source_data/VerveStacks_UGA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\VerveStacks\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16D1EB19-C116-4CBF-A546-853908E2C061}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C461833-168F-4FF5-9A33-3FF90D50C472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="weo_pg" sheetId="13" r:id="rId1"/>
-    <sheet name="re_targets" sheetId="12" r:id="rId2"/>
-    <sheet name="ccs_retrofits" sheetId="11" r:id="rId3"/>
-    <sheet name="Calibration" sheetId="10" r:id="rId4"/>
-    <sheet name="existing_stock" sheetId="9" r:id="rId5"/>
+    <sheet name="weo_pg" sheetId="23" r:id="rId1"/>
+    <sheet name="re_targets" sheetId="22" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="21" r:id="rId3"/>
+    <sheet name="Calibration" sheetId="20" r:id="rId4"/>
+    <sheet name="existing_stock" sheetId="19" r:id="rId5"/>
     <sheet name="historical_data_long" sheetId="5" r:id="rId6"/>
     <sheet name="historical_data" sheetId="4" r:id="rId7"/>
     <sheet name="system_settings" sheetId="1" r:id="rId8"/>
@@ -910,7 +910,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7952E4D1-FED1-0457-0928-FEE7F2A04B0B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97D6EECB-73B6-1BAB-DF60-732FF4FE9A07}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -965,7 +965,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D0B8D4E-B3CA-7924-11EC-42DB91D7FCC8}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91A6A0D6-FF48-1EAE-93C0-EB81132F0ABC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1316,7 +1316,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4DD87CF-AAE7-40E6-9EC0-26F14E71D604}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66528C0-66CE-45F1-BACB-C611E430B1C9}">
   <dimension ref="B2:I129"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4444,7 +4444,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79D3C383-8775-4383-B8DB-25793D59309F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53505CA9-C4A1-404C-965E-56875C19A0C5}">
   <dimension ref="B2:L10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4739,7 +4739,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87405E25-5EE2-48C3-9AD6-F6BB8E89148A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C7A6280-9FD1-4802-855D-D6326B68FBF2}">
   <dimension ref="B2:J6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4870,7 +4870,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62F6509D-5E03-4E21-9970-7AF99A8235CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{237B5177-7B6D-4322-B063-249498EDE9A2}">
   <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -5220,7 +5220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33E473F0-9F54-43F3-AC33-525EBCFAD964}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0193C8C6-C716-42A5-9D12-790173547E2A}">
   <dimension ref="A1:Y48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
